--- a/Data Files/Backoffce/GestaoRegularizacaoIncidencias/GestaoRegularizacaoIncidencias.xlsx
+++ b/Data Files/Backoffce/GestaoRegularizacaoIncidencias/GestaoRegularizacaoIncidencias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\GestaoRegularizacaoIncidencias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{1C9C1637-6FB6-4D72-B96F-34A8BB690371}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{DC2E2DFB-7674-49A0-8FDC-87DB50122126}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
     <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="1" r:id="rId2" sheetId="4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">RegularizarIncidencias!$A$1:$D$7</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">RegularizarIncidencias!$A$1:$D$1</definedName>
     <definedName name="Base">#REF!</definedName>
     <definedName name="TAB">#REF!</definedName>
   </definedNames>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="158">
   <si>
     <t>Status</t>
   </si>
@@ -54,121 +54,457 @@
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>734926532</t>
-  </si>
-  <si>
-    <t>614250912</t>
-  </si>
-  <si>
-    <t>667924959</t>
-  </si>
-  <si>
-    <t>666820059</t>
-  </si>
-  <si>
-    <t>658954668</t>
-  </si>
-  <si>
-    <t>636321196</t>
-  </si>
-  <si>
-    <t>625972835</t>
-  </si>
-  <si>
-    <t>624799163</t>
-  </si>
-  <si>
-    <t>620434294</t>
-  </si>
-  <si>
-    <t>580996829</t>
-  </si>
-  <si>
-    <t>607945213</t>
-  </si>
-  <si>
-    <t>606561276</t>
-  </si>
-  <si>
-    <t>605218852</t>
-  </si>
-  <si>
-    <t>604936371</t>
-  </si>
-  <si>
-    <t>595842083</t>
-  </si>
-  <si>
-    <t>595258389</t>
-  </si>
-  <si>
-    <t>593505682</t>
-  </si>
-  <si>
-    <t>592785673</t>
-  </si>
-  <si>
-    <t>592548113</t>
-  </si>
-  <si>
-    <t>556826943</t>
-  </si>
-  <si>
-    <t>531580722</t>
-  </si>
-  <si>
-    <t>740007871</t>
-  </si>
-  <si>
-    <t>707050815</t>
-  </si>
-  <si>
-    <t>693380879</t>
-  </si>
-  <si>
-    <t>696655434</t>
-  </si>
-  <si>
-    <t>682543297</t>
-  </si>
-  <si>
-    <t>619449519</t>
-  </si>
-  <si>
-    <t>634854420</t>
-  </si>
-  <si>
-    <t>667303873</t>
-  </si>
-  <si>
-    <t>646903751</t>
-  </si>
-  <si>
-    <t>640511311</t>
-  </si>
-  <si>
-    <t>640475665</t>
-  </si>
-  <si>
-    <t>623942723</t>
-  </si>
-  <si>
-    <t>740701622</t>
-  </si>
-  <si>
-    <t>723916874</t>
-  </si>
-  <si>
-    <t>697395386</t>
-  </si>
-  <si>
-    <t>707871319</t>
+    <t>731080671</t>
+  </si>
+  <si>
+    <t>845321870</t>
+  </si>
+  <si>
+    <t>871908012</t>
+  </si>
+  <si>
+    <t>874983087</t>
+  </si>
+  <si>
+    <t>874983079</t>
+  </si>
+  <si>
+    <t>897992024</t>
+  </si>
+  <si>
+    <t>897984401</t>
+  </si>
+  <si>
+    <t>897981894</t>
+  </si>
+  <si>
+    <t>889699660</t>
+  </si>
+  <si>
+    <t>889226555</t>
+  </si>
+  <si>
+    <t>889132456</t>
+  </si>
+  <si>
+    <t>784793808</t>
+  </si>
+  <si>
+    <t>828729180</t>
+  </si>
+  <si>
+    <t>827519814</t>
+  </si>
+  <si>
+    <t>819144985</t>
+  </si>
+  <si>
+    <t>810768550</t>
+  </si>
+  <si>
+    <t>813047499</t>
+  </si>
+  <si>
+    <t>812437386</t>
+  </si>
+  <si>
+    <t>782866937</t>
+  </si>
+  <si>
+    <t>781482942</t>
+  </si>
+  <si>
+    <t>771226374</t>
+  </si>
+  <si>
+    <t>778784458</t>
+  </si>
+  <si>
+    <t>773503614</t>
+  </si>
+  <si>
+    <t>771910209</t>
+  </si>
+  <si>
+    <t>764430835</t>
+  </si>
+  <si>
+    <t>763166448</t>
+  </si>
+  <si>
+    <t>751739289</t>
+  </si>
+  <si>
+    <t>749770982</t>
+  </si>
+  <si>
+    <t>743039830</t>
+  </si>
+  <si>
+    <t>739761744</t>
+  </si>
+  <si>
+    <t>737880710</t>
+  </si>
+  <si>
+    <t>734907227</t>
+  </si>
+  <si>
+    <t>177091778</t>
+  </si>
+  <si>
+    <t>692586377</t>
+  </si>
+  <si>
+    <t>698341454</t>
+  </si>
+  <si>
+    <t>716652395</t>
+  </si>
+  <si>
+    <t>701090379</t>
+  </si>
+  <si>
+    <t>698879370</t>
+  </si>
+  <si>
+    <t>177720392</t>
+  </si>
+  <si>
+    <t>178724997</t>
+  </si>
+  <si>
+    <t>820468571</t>
+  </si>
+  <si>
+    <t>808970382</t>
+  </si>
+  <si>
+    <t>890053592</t>
+  </si>
+  <si>
+    <t>876764170</t>
+  </si>
+  <si>
+    <t>861943714</t>
+  </si>
+  <si>
+    <t>865378057</t>
+  </si>
+  <si>
+    <t>889808931</t>
+  </si>
+  <si>
+    <t>179790575</t>
+  </si>
+  <si>
+    <t>178829416</t>
+  </si>
+  <si>
+    <t>847402009</t>
+  </si>
+  <si>
+    <t>775593464</t>
+  </si>
+  <si>
+    <t>794196117</t>
+  </si>
+  <si>
+    <t>792127361</t>
+  </si>
+  <si>
+    <t>773426014</t>
+  </si>
+  <si>
+    <t>768086575</t>
+  </si>
+  <si>
+    <t>772796904</t>
+  </si>
+  <si>
+    <t>765675404</t>
+  </si>
+  <si>
+    <t>754172793</t>
+  </si>
+  <si>
+    <t>704544760</t>
+  </si>
+  <si>
+    <t>738767015</t>
+  </si>
+  <si>
+    <t>748768557</t>
+  </si>
+  <si>
+    <t>699870378</t>
+  </si>
+  <si>
+    <t>677601555</t>
+  </si>
+  <si>
+    <t>690083500</t>
+  </si>
+  <si>
+    <t>864101583</t>
+  </si>
+  <si>
+    <t>874459401</t>
+  </si>
+  <si>
+    <t>872425842</t>
+  </si>
+  <si>
+    <t>849655778</t>
+  </si>
+  <si>
+    <t>813781154</t>
+  </si>
+  <si>
+    <t>809310133</t>
+  </si>
+  <si>
+    <t>749052399</t>
+  </si>
+  <si>
+    <t>770082422</t>
+  </si>
+  <si>
+    <t>891683397</t>
+  </si>
+  <si>
+    <t>726591377</t>
+  </si>
+  <si>
+    <t>765687136</t>
+  </si>
+  <si>
+    <t>764441279</t>
+  </si>
+  <si>
+    <t>761215080</t>
+  </si>
+  <si>
+    <t>750620357</t>
+  </si>
+  <si>
+    <t>724977644</t>
+  </si>
+  <si>
+    <t>721856643</t>
+  </si>
+  <si>
+    <t>703023675</t>
+  </si>
+  <si>
+    <t>700247004</t>
+  </si>
+  <si>
+    <t>690545987</t>
+  </si>
+  <si>
+    <t>648233470</t>
+  </si>
+  <si>
+    <t>178025437</t>
+  </si>
+  <si>
+    <t>812732489</t>
+  </si>
+  <si>
+    <t>766947182</t>
+  </si>
+  <si>
+    <t>781505882</t>
+  </si>
+  <si>
+    <t>778688717</t>
+  </si>
+  <si>
+    <t>767112745</t>
+  </si>
+  <si>
+    <t>847915273</t>
+  </si>
+  <si>
+    <t>809063278</t>
+  </si>
+  <si>
+    <t>808688943</t>
+  </si>
+  <si>
+    <t>801275839</t>
+  </si>
+  <si>
+    <t>801009345</t>
+  </si>
+  <si>
+    <t>771587809</t>
+  </si>
+  <si>
+    <t>787663909</t>
+  </si>
+  <si>
+    <t>790840593</t>
+  </si>
+  <si>
+    <t>788656548</t>
+  </si>
+  <si>
+    <t>774762201</t>
+  </si>
+  <si>
+    <t>775591807</t>
+  </si>
+  <si>
+    <t>863654103</t>
+  </si>
+  <si>
+    <t>179301217</t>
+  </si>
+  <si>
+    <t>178838508</t>
+  </si>
+  <si>
+    <t>178838482</t>
+  </si>
+  <si>
+    <t>178838284</t>
+  </si>
+  <si>
+    <t>178838342</t>
+  </si>
+  <si>
+    <t>178838334</t>
+  </si>
+  <si>
+    <t>178838326</t>
+  </si>
+  <si>
+    <t>178838318</t>
+  </si>
+  <si>
+    <t>178827667</t>
+  </si>
+  <si>
+    <t>896459314</t>
+  </si>
+  <si>
+    <t>890530326</t>
+  </si>
+  <si>
+    <t>890166782</t>
+  </si>
+  <si>
+    <t>890126927</t>
+  </si>
+  <si>
+    <t>888870320</t>
+  </si>
+  <si>
+    <t>889887398</t>
+  </si>
+  <si>
+    <t>889839647</t>
+  </si>
+  <si>
+    <t>889800631</t>
+  </si>
+  <si>
+    <t>889536961</t>
+  </si>
+  <si>
+    <t>887798886</t>
+  </si>
+  <si>
+    <t>868435516</t>
+  </si>
+  <si>
+    <t>867182580</t>
+  </si>
+  <si>
+    <t>867064168</t>
+  </si>
+  <si>
+    <t>864971654</t>
+  </si>
+  <si>
+    <t>848008573</t>
+  </si>
+  <si>
+    <t>850209283</t>
+  </si>
+  <si>
+    <t>847639576</t>
+  </si>
+  <si>
+    <t>842237335</t>
+  </si>
+  <si>
+    <t>841601259</t>
+  </si>
+  <si>
+    <t>841200177</t>
+  </si>
+  <si>
+    <t>840752640</t>
+  </si>
+  <si>
+    <t>836960413</t>
+  </si>
+  <si>
+    <t>835756911</t>
+  </si>
+  <si>
+    <t>816001584</t>
+  </si>
+  <si>
+    <t>827141767</t>
+  </si>
+  <si>
+    <t>832868883</t>
+  </si>
+  <si>
+    <t>830981217</t>
+  </si>
+  <si>
+    <t>821123514</t>
+  </si>
+  <si>
+    <t>820617722</t>
+  </si>
+  <si>
+    <t>818737359</t>
+  </si>
+  <si>
+    <t>818022430</t>
+  </si>
+  <si>
+    <t>817702800</t>
+  </si>
+  <si>
+    <t>817254935</t>
+  </si>
+  <si>
+    <t>813624206</t>
+  </si>
+  <si>
+    <t>803129992</t>
+  </si>
+  <si>
+    <t>802849392</t>
+  </si>
+  <si>
+    <t>801728324</t>
   </si>
   <si>
     <t>Processado</t>
   </si>
   <si>
     <t>Tela 'CONSULTA DE DOCUMENTOS A REGULARIZAR': O recibo a ser regularizado já está QUITADO! Confirmada regularização do documento</t>
+  </si>
+  <si>
+    <t>Alerta: Tela 'CONSULTA DE DOCUMENTOS A REGULARIZAR':  Nenhum registro encontrado para os parâmetros informados!</t>
   </si>
 </sst>
 </file>
@@ -179,7 +515,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,12 +537,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -283,7 +613,7 @@
     <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="43"/>
     <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="164"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="4" fontId="2" numFmtId="49" xfId="1">
       <alignment horizontal="center" vertical="center"/>
@@ -297,20 +627,14 @@
     <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="left"/>
@@ -335,9 +659,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
@@ -375,7 +699,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
@@ -481,7 +805,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -623,7 +947,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -634,551 +958,2105 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="3" width="38.0" collapsed="true"/>
     <col min="2" max="2" customWidth="true" style="4" width="64.85546875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="6" width="14.5703125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="10" width="124.28515625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="14.5703125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="8" width="124.28515625" collapsed="true"/>
     <col min="5" max="16384" style="4" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row customFormat="1" r="1" s="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D3" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D4" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D5" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D6" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D7" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D8" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D9" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D10" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D11" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D12" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D13" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D14" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D15" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D16" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D17" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D18" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D19" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D20" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D21" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D22" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>45</v>
+        <v>155</v>
+      </c>
+      <c r="D23" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D38" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D39" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D41" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D42" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D43" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D44" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D45" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D46" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D47" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D48" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D49" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D50" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D51" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D52" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D53" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D54" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D55" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D56" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D57" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D58" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D59" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D60" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D61" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D62" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D63" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D64" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D65" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D66" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D67" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D68" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D69" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D70" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D71" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D72" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D73" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D74" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D75" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D76" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D77" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D78" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D79" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D80" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D81" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D82" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D83" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D84" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D85" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D86" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D87" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D88" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D89" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D90" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D91" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D92" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D93" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D94" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D95" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D96" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D97" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D98" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D99" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D100" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D101" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D102" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D103" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D104" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D105" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D106" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D107" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D108" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D109" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D110" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D111" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D112" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D113" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5" t="s">
+      <c r="B114" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D114" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D38" t="s">
+      <c r="B115" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D115" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="B116" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D116" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D117" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D118" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D119" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D120" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D121" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D122" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D123" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D124" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D125" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D126" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D127" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D128" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D129" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D130" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D131" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D132" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D133" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D134" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D135" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D136" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D137" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D138" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D139" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D140" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D141" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D142" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D143" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D144" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D145" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D146" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D147" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D148" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D149" t="s">
+        <v>157</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
   <pageSetup horizontalDpi="300" orientation="portrait" paperSize="9" r:id="rId1" verticalDpi="300"/>
   <headerFooter>
@@ -1199,31 +3077,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>